--- a/SJ/SB02_NOW/SB02_ComparisonTable.xlsx
+++ b/SJ/SB02_NOW/SB02_ComparisonTable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\產學合作\深峻\SB02_NOW\RAW\sliding_window_results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\sb01_dashboard-main\SJ\SB02_NOW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8808AE33-0523-4327-8B66-8FF8CEF0089B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31719D53-1686-4FD7-9377-9296B958FA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="15430" windowHeight="12110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1F" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="162">
   <si>
     <t>DCC_name</t>
   </si>
@@ -509,6 +509,10 @@
   </si>
   <si>
     <t>Inappropriate</t>
+  </si>
+  <si>
+    <t>Inappropriate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1027,9 +1031,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主題">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1067,7 +1071,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1173,7 +1177,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1315,7 +1319,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1324,19 +1328,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K33"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" style="7" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="7" customWidth="1"/>
-    <col min="7" max="9" width="10.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" style="7" customWidth="1"/>
+    <col min="7" max="9" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1357,11 +1361,13 @@
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
       <c r="J1" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="K1" s="30"/>
-    </row>
-    <row r="2" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>161</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1382,7 +1388,7 @@
       </c>
       <c r="K2" s="37"/>
     </row>
-    <row r="3" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1407,7 +1413,7 @@
       </c>
       <c r="K3" s="37"/>
     </row>
-    <row r="4" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -1432,7 +1438,7 @@
       </c>
       <c r="K4" s="37"/>
     </row>
-    <row r="5" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -1453,7 +1459,7 @@
       </c>
       <c r="K5" s="37"/>
     </row>
-    <row r="6" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -1474,7 +1480,7 @@
       </c>
       <c r="K6" s="37"/>
     </row>
-    <row r="7" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -1495,7 +1501,7 @@
       </c>
       <c r="K7" s="37"/>
     </row>
-    <row r="8" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -1516,7 +1522,7 @@
       </c>
       <c r="K8" s="37"/>
     </row>
-    <row r="9" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -1547,7 +1553,7 @@
       </c>
       <c r="K9" s="37"/>
     </row>
-    <row r="10" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>20</v>
       </c>
@@ -1568,7 +1574,7 @@
       </c>
       <c r="K10" s="37"/>
     </row>
-    <row r="11" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
@@ -1589,7 +1595,7 @@
       </c>
       <c r="K11" s="37"/>
     </row>
-    <row r="12" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
@@ -1614,7 +1620,7 @@
       </c>
       <c r="K12" s="37"/>
     </row>
-    <row r="13" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -1639,7 +1645,7 @@
       </c>
       <c r="K13" s="37"/>
     </row>
-    <row r="14" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -1668,7 +1674,7 @@
       </c>
       <c r="K14" s="37"/>
     </row>
-    <row r="15" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="4" t="s">
         <v>25</v>
       </c>
@@ -1689,7 +1695,7 @@
       </c>
       <c r="K15" s="40"/>
     </row>
-    <row r="16" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="4" t="s">
         <v>28</v>
       </c>
@@ -1710,7 +1716,7 @@
       </c>
       <c r="K16" s="40"/>
     </row>
-    <row r="17" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
         <v>30</v>
       </c>
@@ -1731,7 +1737,7 @@
       </c>
       <c r="K17" s="40"/>
     </row>
-    <row r="18" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="4" t="s">
         <v>31</v>
       </c>
@@ -1752,7 +1758,7 @@
       </c>
       <c r="K18" s="40"/>
     </row>
-    <row r="19" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="4" t="s">
         <v>32</v>
       </c>
@@ -1773,7 +1779,7 @@
       </c>
       <c r="K19" s="40"/>
     </row>
-    <row r="20" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="4" t="s">
         <v>34</v>
       </c>
@@ -1794,7 +1800,7 @@
       </c>
       <c r="K20" s="40"/>
     </row>
-    <row r="21" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="4" t="s">
         <v>35</v>
       </c>
@@ -1815,7 +1821,7 @@
       </c>
       <c r="K21" s="40"/>
     </row>
-    <row r="22" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="4" t="s">
         <v>36</v>
       </c>
@@ -1836,7 +1842,7 @@
       </c>
       <c r="K22" s="40"/>
     </row>
-    <row r="23" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
         <v>37</v>
       </c>
@@ -1857,7 +1863,7 @@
       </c>
       <c r="K23" s="40"/>
     </row>
-    <row r="24" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
         <v>38</v>
       </c>
@@ -1878,7 +1884,7 @@
       </c>
       <c r="K24" s="45"/>
     </row>
-    <row r="25" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
         <v>39</v>
       </c>
@@ -1907,7 +1913,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="4" t="s">
         <v>42</v>
       </c>
@@ -1928,7 +1934,7 @@
       </c>
       <c r="K26" s="46"/>
     </row>
-    <row r="27" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="4" t="s">
         <v>43</v>
       </c>
@@ -1949,7 +1955,7 @@
       </c>
       <c r="K27" s="40"/>
     </row>
-    <row r="28" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="4" t="s">
         <v>44</v>
       </c>
@@ -1970,7 +1976,7 @@
       </c>
       <c r="K28" s="40"/>
     </row>
-    <row r="29" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
         <v>46</v>
       </c>
@@ -1991,7 +1997,7 @@
       </c>
       <c r="K29" s="40"/>
     </row>
-    <row r="30" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="4" t="s">
         <v>47</v>
       </c>
@@ -2012,7 +2018,7 @@
       </c>
       <c r="K30" s="40"/>
     </row>
-    <row r="31" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="6" t="s">
         <v>48</v>
       </c>
@@ -2033,7 +2039,7 @@
       </c>
       <c r="K31" s="43"/>
     </row>
-    <row r="32" spans="1:11" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="6" t="s">
         <v>51</v>
       </c>
@@ -2054,7 +2060,7 @@
       </c>
       <c r="K32" s="43"/>
     </row>
-    <row r="33" ht="16.8" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="17.5" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2064,18 +2070,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I32"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2094,11 +2100,11 @@
       </c>
       <c r="G1" s="13"/>
       <c r="H1" s="30" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I1" s="30"/>
     </row>
-    <row r="2" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
@@ -2117,7 +2123,7 @@
       </c>
       <c r="I2" s="49"/>
     </row>
-    <row r="3" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -2146,7 +2152,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -2171,7 +2177,7 @@
       </c>
       <c r="I4" s="50"/>
     </row>
-    <row r="5" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -2194,7 +2200,7 @@
       </c>
       <c r="I5" s="37"/>
     </row>
-    <row r="6" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>58</v>
       </c>
@@ -2213,7 +2219,7 @@
       </c>
       <c r="I6" s="37"/>
     </row>
-    <row r="7" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -2232,7 +2238,7 @@
       </c>
       <c r="I7" s="37"/>
     </row>
-    <row r="8" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
@@ -2251,7 +2257,7 @@
       </c>
       <c r="I8" s="37"/>
     </row>
-    <row r="9" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>59</v>
       </c>
@@ -2270,7 +2276,7 @@
       </c>
       <c r="I9" s="37"/>
     </row>
-    <row r="10" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>60</v>
       </c>
@@ -2289,7 +2295,7 @@
       </c>
       <c r="I10" s="37"/>
     </row>
-    <row r="11" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -2312,7 +2318,7 @@
       </c>
       <c r="I11" s="37"/>
     </row>
-    <row r="12" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -2335,7 +2341,7 @@
       </c>
       <c r="I12" s="37"/>
     </row>
-    <row r="13" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -2354,7 +2360,7 @@
       </c>
       <c r="I13" s="37"/>
     </row>
-    <row r="14" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -2373,7 +2379,7 @@
       </c>
       <c r="I14" s="37"/>
     </row>
-    <row r="15" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -2392,7 +2398,7 @@
       </c>
       <c r="I15" s="37"/>
     </row>
-    <row r="16" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>25</v>
       </c>
@@ -2411,7 +2417,7 @@
       </c>
       <c r="I16" s="37"/>
     </row>
-    <row r="17" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
         <v>62</v>
       </c>
@@ -2430,7 +2436,7 @@
       </c>
       <c r="I17" s="37"/>
     </row>
-    <row r="18" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="4" t="s">
         <v>39</v>
       </c>
@@ -2449,7 +2455,7 @@
       </c>
       <c r="I18" s="40"/>
     </row>
-    <row r="19" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="4" t="s">
         <v>34</v>
       </c>
@@ -2468,7 +2474,7 @@
       </c>
       <c r="I19" s="40"/>
     </row>
-    <row r="20" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="4" t="s">
         <v>31</v>
       </c>
@@ -2487,7 +2493,7 @@
       </c>
       <c r="I20" s="40"/>
     </row>
-    <row r="21" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="4" t="s">
         <v>28</v>
       </c>
@@ -2510,7 +2516,7 @@
       </c>
       <c r="I21" s="40"/>
     </row>
-    <row r="22" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="4" t="s">
         <v>30</v>
       </c>
@@ -2529,7 +2535,7 @@
       </c>
       <c r="I22" s="45"/>
     </row>
-    <row r="23" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
         <v>67</v>
       </c>
@@ -2552,7 +2558,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
         <v>35</v>
       </c>
@@ -2575,7 +2581,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
         <v>32</v>
       </c>
@@ -2594,7 +2600,7 @@
       </c>
       <c r="I25" s="46"/>
     </row>
-    <row r="26" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="4" t="s">
         <v>36</v>
       </c>
@@ -2613,7 +2619,7 @@
       </c>
       <c r="I26" s="40"/>
     </row>
-    <row r="27" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="4" t="s">
         <v>47</v>
       </c>
@@ -2632,7 +2638,7 @@
       </c>
       <c r="I27" s="40"/>
     </row>
-    <row r="28" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="4" t="s">
         <v>37</v>
       </c>
@@ -2651,7 +2657,7 @@
       </c>
       <c r="I28" s="40"/>
     </row>
-    <row r="29" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
         <v>43</v>
       </c>
@@ -2670,7 +2676,7 @@
       </c>
       <c r="I29" s="40"/>
     </row>
-    <row r="30" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="4" t="s">
         <v>44</v>
       </c>
@@ -2689,7 +2695,7 @@
       </c>
       <c r="I30" s="40"/>
     </row>
-    <row r="31" spans="1:9" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="4" t="s">
         <v>46</v>
       </c>
@@ -2708,7 +2714,7 @@
       </c>
       <c r="I31" s="40"/>
     </row>
-    <row r="32" spans="1:9" ht="16.8" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:9" ht="17.5" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2718,17 +2724,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2750,7 +2756,7 @@
       </c>
       <c r="H1" s="30"/>
     </row>
-    <row r="2" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>73</v>
       </c>
@@ -2772,7 +2778,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>77</v>
       </c>
@@ -2790,7 +2796,7 @@
       </c>
       <c r="H3" s="50"/>
     </row>
-    <row r="4" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -2808,7 +2814,7 @@
       </c>
       <c r="H4" s="49"/>
     </row>
-    <row r="5" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
@@ -2830,7 +2836,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -2848,7 +2854,7 @@
       </c>
       <c r="H6" s="50"/>
     </row>
-    <row r="7" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -2866,7 +2872,7 @@
       </c>
       <c r="H7" s="37"/>
     </row>
-    <row r="8" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>58</v>
       </c>
@@ -2888,7 +2894,7 @@
       </c>
       <c r="H8" s="37"/>
     </row>
-    <row r="9" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>85</v>
       </c>
@@ -2906,7 +2912,7 @@
       </c>
       <c r="H9" s="49"/>
     </row>
-    <row r="10" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>59</v>
       </c>
@@ -2928,7 +2934,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>87</v>
       </c>
@@ -2946,7 +2952,7 @@
       </c>
       <c r="H11" s="50"/>
     </row>
-    <row r="12" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
@@ -2964,7 +2970,7 @@
       </c>
       <c r="H12" s="37"/>
     </row>
-    <row r="13" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
@@ -2982,7 +2988,7 @@
       </c>
       <c r="H13" s="37"/>
     </row>
-    <row r="14" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>5</v>
       </c>
@@ -3000,7 +3006,7 @@
       </c>
       <c r="H14" s="37"/>
     </row>
-    <row r="15" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>15</v>
       </c>
@@ -3022,7 +3028,7 @@
       </c>
       <c r="H15" s="37"/>
     </row>
-    <row r="16" spans="1:8" ht="16.8" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:8" ht="17.5" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3032,18 +3038,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3065,7 +3071,7 @@
       </c>
       <c r="H1" s="30"/>
     </row>
-    <row r="2" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>85</v>
       </c>
@@ -3083,7 +3089,7 @@
       </c>
       <c r="H2" s="49"/>
     </row>
-    <row r="3" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -3105,7 +3111,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>20</v>
       </c>
@@ -3123,7 +3129,7 @@
       </c>
       <c r="H4" s="50"/>
     </row>
-    <row r="5" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -3141,7 +3147,7 @@
       </c>
       <c r="H5" s="37"/>
     </row>
-    <row r="6" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -3163,7 +3169,7 @@
       </c>
       <c r="H6" s="37"/>
     </row>
-    <row r="7" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -3181,7 +3187,7 @@
       </c>
       <c r="H7" s="37"/>
     </row>
-    <row r="8" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -3199,7 +3205,7 @@
       </c>
       <c r="H8" s="37"/>
     </row>
-    <row r="9" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -3217,7 +3223,7 @@
       </c>
       <c r="H9" s="37"/>
     </row>
-    <row r="10" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -3235,7 +3241,7 @@
       </c>
       <c r="H10" s="37"/>
     </row>
-    <row r="11" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -3253,7 +3259,7 @@
       </c>
       <c r="H11" s="37"/>
     </row>
-    <row r="12" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
@@ -3275,7 +3281,7 @@
       </c>
       <c r="H12" s="37"/>
     </row>
-    <row r="13" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
@@ -3293,7 +3299,7 @@
       </c>
       <c r="H13" s="37"/>
     </row>
-    <row r="14" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>59</v>
       </c>
@@ -3311,7 +3317,7 @@
       </c>
       <c r="H14" s="49"/>
     </row>
-    <row r="15" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>77</v>
       </c>
@@ -3337,7 +3343,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="4" t="s">
         <v>87</v>
       </c>
@@ -3355,7 +3361,7 @@
       </c>
       <c r="H16" s="53"/>
     </row>
-    <row r="17" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
         <v>99</v>
       </c>
@@ -3381,7 +3387,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="4" t="s">
         <v>42</v>
       </c>
@@ -3399,7 +3405,7 @@
       </c>
       <c r="H18" s="46"/>
     </row>
-    <row r="19" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="4" t="s">
         <v>62</v>
       </c>
@@ -3421,7 +3427,7 @@
       </c>
       <c r="H19" s="40"/>
     </row>
-    <row r="20" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="4" t="s">
         <v>39</v>
       </c>
@@ -3439,7 +3445,7 @@
       </c>
       <c r="H20" s="40"/>
     </row>
-    <row r="21" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="4" t="s">
         <v>28</v>
       </c>
@@ -3457,7 +3463,7 @@
       </c>
       <c r="H21" s="45"/>
     </row>
-    <row r="22" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="4" t="s">
         <v>30</v>
       </c>
@@ -3483,7 +3489,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
         <v>32</v>
       </c>
@@ -3501,7 +3507,7 @@
       </c>
       <c r="H23" s="46"/>
     </row>
-    <row r="24" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
         <v>34</v>
       </c>
@@ -3519,7 +3525,7 @@
       </c>
       <c r="H24" s="45"/>
     </row>
-    <row r="25" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
         <v>31</v>
       </c>
@@ -3541,7 +3547,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="4" t="s">
         <v>35</v>
       </c>
@@ -3559,7 +3565,7 @@
       </c>
       <c r="H26" s="53"/>
     </row>
-    <row r="27" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="4" t="s">
         <v>36</v>
       </c>
@@ -3581,7 +3587,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="4" t="s">
         <v>43</v>
       </c>
@@ -3607,7 +3613,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
         <v>44</v>
       </c>
@@ -3629,7 +3635,7 @@
       </c>
       <c r="H29" s="46"/>
     </row>
-    <row r="30" spans="1:8" ht="16.8" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:8" ht="17.5" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3639,18 +3645,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3671,7 +3677,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>107</v>
       </c>
@@ -3692,7 +3698,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>111</v>
       </c>
@@ -3709,7 +3715,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>112</v>
       </c>
@@ -3726,7 +3732,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>114</v>
       </c>
@@ -3747,7 +3753,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>116</v>
       </c>
@@ -3770,7 +3776,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>118</v>
       </c>
@@ -3791,7 +3797,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="4" t="s">
         <v>30</v>
       </c>
@@ -3808,7 +3814,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="4" t="s">
         <v>122</v>
       </c>
@@ -3825,7 +3831,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="6" t="s">
         <v>5</v>
       </c>
@@ -3842,7 +3848,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="6" t="s">
         <v>13</v>
       </c>
@@ -3859,7 +3865,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="6" t="s">
         <v>14</v>
       </c>
@@ -3876,7 +3882,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="6" t="s">
         <v>17</v>
       </c>
@@ -3893,7 +3899,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="6" t="s">
         <v>77</v>
       </c>
@@ -3910,7 +3916,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="6" t="s">
         <v>12</v>
       </c>
@@ -3927,7 +3933,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="6" t="s">
         <v>21</v>
       </c>
@@ -3950,7 +3956,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="6" t="s">
         <v>22</v>
       </c>
@@ -3971,7 +3977,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="6" t="s">
         <v>23</v>
       </c>
@@ -3992,7 +3998,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="6" t="s">
         <v>24</v>
       </c>
@@ -4009,7 +4015,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="6" t="s">
         <v>58</v>
       </c>
@@ -4026,7 +4032,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="6" t="s">
         <v>8</v>
       </c>
@@ -4043,7 +4049,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="6" t="s">
         <v>20</v>
       </c>
@@ -4060,7 +4066,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="6" t="s">
         <v>15</v>
       </c>
@@ -4081,7 +4087,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>87</v>
       </c>
@@ -4098,7 +4104,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
         <v>25</v>
       </c>
@@ -4115,7 +4121,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
         <v>62</v>
       </c>
@@ -4132,7 +4138,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
         <v>42</v>
       </c>
@@ -4153,7 +4159,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
         <v>51</v>
       </c>
@@ -4170,7 +4176,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
         <v>39</v>
       </c>
@@ -4191,7 +4197,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
         <v>67</v>
       </c>
@@ -4212,7 +4218,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
         <v>32</v>
       </c>
@@ -4229,7 +4235,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
         <v>34</v>
       </c>
@@ -4250,7 +4256,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
         <v>31</v>
       </c>
@@ -4267,7 +4273,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
         <v>35</v>
       </c>
@@ -4284,7 +4290,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
         <v>37</v>
       </c>
@@ -4301,7 +4307,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.8" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="17.5" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A36" s="2" t="s">
         <v>43</v>
       </c>
@@ -4331,18 +4337,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="10.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.21875" customWidth="1"/>
+    <col min="1" max="1" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4366,7 +4372,7 @@
       <c r="I1" s="30"/>
       <c r="J1" s="30"/>
     </row>
-    <row r="2" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -4390,7 +4396,7 @@
       </c>
       <c r="J2" s="37"/>
     </row>
-    <row r="3" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>58</v>
       </c>
@@ -4414,7 +4420,7 @@
       </c>
       <c r="J3" s="37"/>
     </row>
-    <row r="4" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>85</v>
       </c>
@@ -4434,7 +4440,7 @@
       <c r="I4" s="50"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -4458,7 +4464,7 @@
       <c r="I5" s="37"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -4478,7 +4484,7 @@
       <c r="I6" s="37"/>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -4498,7 +4504,7 @@
       <c r="I7" s="37"/>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -4518,7 +4524,7 @@
       <c r="I8" s="37"/>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -4538,7 +4544,7 @@
       <c r="I9" s="37"/>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -4558,7 +4564,7 @@
       <c r="I10" s="37"/>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -4578,7 +4584,7 @@
       <c r="I11" s="37"/>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
@@ -4598,7 +4604,7 @@
       <c r="I12" s="37"/>
       <c r="J12" s="3"/>
     </row>
-    <row r="13" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
@@ -4622,7 +4628,7 @@
       <c r="I13" s="49"/>
       <c r="J13" s="3"/>
     </row>
-    <row r="14" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>77</v>
       </c>
@@ -4646,7 +4652,7 @@
       </c>
       <c r="J14" s="37"/>
     </row>
-    <row r="15" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>60</v>
       </c>
@@ -4666,7 +4672,7 @@
       <c r="I15" s="56"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="4" t="s">
         <v>48</v>
       </c>
@@ -4690,7 +4696,7 @@
       </c>
       <c r="J16" s="40"/>
     </row>
-    <row r="17" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A17" s="4" t="s">
         <v>51</v>
       </c>
@@ -4710,7 +4716,7 @@
       <c r="I17" s="46"/>
       <c r="J17" s="5"/>
     </row>
-    <row r="18" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A18" s="4" t="s">
         <v>25</v>
       </c>
@@ -4730,7 +4736,7 @@
       <c r="I18" s="40"/>
       <c r="J18" s="5"/>
     </row>
-    <row r="19" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="4" t="s">
         <v>42</v>
       </c>
@@ -4750,7 +4756,7 @@
       <c r="I19" s="40"/>
       <c r="J19" s="5"/>
     </row>
-    <row r="20" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A20" s="4" t="s">
         <v>62</v>
       </c>
@@ -4770,7 +4776,7 @@
       <c r="I20" s="40"/>
       <c r="J20" s="5"/>
     </row>
-    <row r="21" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="4" t="s">
         <v>39</v>
       </c>
@@ -4790,7 +4796,7 @@
       <c r="I21" s="40"/>
       <c r="J21" s="5"/>
     </row>
-    <row r="22" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="4" t="s">
         <v>28</v>
       </c>
@@ -4810,7 +4816,7 @@
       <c r="I22" s="40"/>
       <c r="J22" s="5"/>
     </row>
-    <row r="23" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
         <v>30</v>
       </c>
@@ -4830,7 +4836,7 @@
       <c r="I23" s="40"/>
       <c r="J23" s="5"/>
     </row>
-    <row r="24" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
         <v>67</v>
       </c>
@@ -4850,7 +4856,7 @@
       <c r="I24" s="40"/>
       <c r="J24" s="5"/>
     </row>
-    <row r="25" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
         <v>32</v>
       </c>
@@ -4870,7 +4876,7 @@
       <c r="I25" s="40"/>
       <c r="J25" s="5"/>
     </row>
-    <row r="26" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A26" s="4" t="s">
         <v>34</v>
       </c>
@@ -4890,7 +4896,7 @@
       <c r="I26" s="40"/>
       <c r="J26" s="5"/>
     </row>
-    <row r="27" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A27" s="4" t="s">
         <v>31</v>
       </c>
@@ -4910,7 +4916,7 @@
       <c r="I27" s="40"/>
       <c r="J27" s="5"/>
     </row>
-    <row r="28" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="4" t="s">
         <v>35</v>
       </c>
@@ -4930,7 +4936,7 @@
       <c r="I28" s="40"/>
       <c r="J28" s="5"/>
     </row>
-    <row r="29" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
         <v>43</v>
       </c>
@@ -4950,7 +4956,7 @@
       <c r="I29" s="45"/>
       <c r="J29" s="57"/>
     </row>
-    <row r="30" spans="1:10" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="4" t="s">
         <v>47</v>
       </c>
@@ -4978,7 +4984,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="16.8" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:10" ht="17.5" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4988,17 +4994,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="14.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.81640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5019,7 +5025,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>58</v>
       </c>
@@ -5036,7 +5042,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -5053,7 +5059,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -5070,7 +5076,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>22</v>
       </c>
@@ -5087,7 +5093,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -5104,7 +5110,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>20</v>
       </c>
@@ -5127,7 +5133,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -5144,7 +5150,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
@@ -5161,7 +5167,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
@@ -5178,7 +5184,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>23</v>
       </c>
@@ -5195,7 +5201,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -5212,7 +5218,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>59</v>
       </c>
@@ -5229,7 +5235,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>77</v>
       </c>
@@ -5250,7 +5256,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="17.399999999999999" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>73</v>
       </c>
@@ -5267,7 +5273,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.8" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:7" ht="17.5" thickTop="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SJ/SB02_NOW/SB02_ComparisonTable.xlsx
+++ b/SJ/SB02_NOW/SB02_ComparisonTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\sb01_dashboard-main\SJ\SB02_NOW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31719D53-1686-4FD7-9377-9296B958FA7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91044E0-6191-42B5-B7F7-613A0EADFF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="15430" windowHeight="12110" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="17260" windowHeight="12110" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1F" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="162">
   <si>
     <t>DCC_name</t>
   </si>
@@ -2102,7 +2102,9 @@
       <c r="H1" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="I1" s="30"/>
+      <c r="I1" s="30" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="2" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
@@ -2754,7 +2756,9 @@
       <c r="G1" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="H1" s="30"/>
+      <c r="H1" s="30" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="2" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
@@ -3069,7 +3073,9 @@
       <c r="G1" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="H1" s="30"/>
+      <c r="H1" s="30" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="2" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
@@ -4369,8 +4375,12 @@
       <c r="H1" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
+      <c r="I1" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="2" spans="1:10" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
